--- a/resul/R1.xlsx
+++ b/resul/R1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/matf8_umsystem_edu/Documents/Desktop/Github/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/matf8_umsystem_edu/Documents/Desktop/github GPV/LLM_GPV/resul/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{8A297284-8668-486A-8A6A-FAC5CE00ABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFD7266A-1402-4403-94A7-399E4F750E4C}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{8A297284-8668-486A-8A6A-FAC5CE00ABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD5EB7C9-FBEF-41A8-A04F-77075CDA431F}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF8A4EFF-0598-4503-AD0D-F51BBA7778E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF8A4EFF-0598-4503-AD0D-F51BBA7778E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -443,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -452,6 +452,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,10 +468,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,15 +788,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72428943-9902-4C15-A3E3-2ED1C66CCDCE}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -812,12 +810,12 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="6" t="s">
         <v>108</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -834,7 +832,7 @@
         <v>0.15400800000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -851,7 +849,7 @@
         <v>0.15400800000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -868,7 +866,7 @@
         <v>0.15400800000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -885,7 +883,7 @@
         <v>0.15400800000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -902,7 +900,7 @@
         <v>0.20401</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -919,7 +917,7 @@
         <v>0.23401</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -936,7 +934,7 @@
         <v>0.25540099999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -953,7 +951,7 @@
         <v>0.235401</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -970,7 +968,7 @@
         <v>0.30055399999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -987,7 +985,7 @@
         <v>0.30055399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1004,7 +1002,7 @@
         <v>0.30055399999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1021,7 +1019,7 @@
         <v>0.35003699999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1038,7 +1036,7 @@
         <v>0.35003699999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -1055,7 +1053,7 @@
         <v>0.45003720000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -1072,7 +1070,7 @@
         <v>0.45003720000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -1089,7 +1087,7 @@
         <v>0.45003720000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
@@ -1106,7 +1104,7 @@
         <v>0.45003720000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -1123,7 +1121,7 @@
         <v>0.48004200000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>8</v>
       </c>
@@ -1140,7 +1138,7 @@
         <v>0.55004200000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
@@ -1157,7 +1155,7 @@
         <v>0.55004200000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -1174,7 +1172,7 @@
         <v>0.55004200000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
@@ -1191,7 +1189,7 @@
         <v>0.55004200000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
@@ -1208,7 +1206,7 @@
         <v>0.60004199999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -1225,7 +1223,7 @@
         <v>0.60004199999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
@@ -1242,7 +1240,7 @@
         <v>0.60004199999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>46</v>
       </c>
@@ -1259,7 +1257,7 @@
         <v>0.60004199999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>50</v>
       </c>
@@ -1276,7 +1274,7 @@
         <v>0.60004199999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
@@ -1293,7 +1291,7 @@
         <v>0.64534199999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
@@ -1310,7 +1308,7 @@
         <v>0.64534199999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>61</v>
       </c>
@@ -1321,7 +1319,7 @@
         <v>0.64534199999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>64</v>
       </c>
